--- a/environment/seed/sources/Shared/Finance/Reporting/Board/Q2 2026/Board performance dashboard - WORKING.xlsx
+++ b/environment/seed/sources/Shared/Finance/Reporting/Board/Q2 2026/Board performance dashboard - WORKING.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Export" sheetId="1" r:id="Rffa92e566c3c4875"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approved Plan" sheetId="2" r:id="Rd60b346bfe034244"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="3" r:id="Re98c8b7edb4a4328"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Units" sheetId="4" r:id="Rde1d577ed6a94d66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash &amp; Capital" sheetId="5" r:id="R9e4c6b92fc4f41b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" r:id="R3ba36e072a814715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Export" sheetId="1" r:id="rId5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approved Plan" sheetId="2" r:id="rId6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="3" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Units" sheetId="4" r:id="rId8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash &amp; Capital" sheetId="5" r:id="rId9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" r:id="rId10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -51,12 +51,12 @@
     </x:font>
     <x:font>
       <x:sz val="9"/>
-      <x:color rgb="FF252321"/>
+      <x:color rgb="FF52655C"/>
       <x:name val="Aptos"/>
     </x:font>
     <x:font>
       <x:sz val="9"/>
-      <x:color rgb="FF52655C"/>
+      <x:color rgb="FF252321"/>
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
@@ -89,12 +89,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF5E8C8"/>
+        <x:fgColor rgb="FFF8F5EF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF8F5EF"/>
+        <x:fgColor rgb="FFF5E8C8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -236,18 +236,18 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -257,7 +257,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{BB842A14-B9D8-4A47-8E28-912BA1736F5E}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{FD67DDC8-6A27-C18A-58B3-AE10B340F265}"/>
 </xltc:personList>
 </file>
 
@@ -472,7 +472,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the Q2 board performance dashboard | Data Export</x:v>
+        <x:v>Q2 board performance dashboard | Data Export</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -488,7 +488,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>LOCKED INPUT SCHEDULE • refreshed from current management workbooks and Vista ERP • Do not edit</x:v>
+        <x:v>REFERENCE SCHEDULE • source and date retained • do not edit</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -542,7 +542,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="22" t="str">
-        <x:v>067-SRC0001</x:v>
+        <x:v>BRD-DATA-0001</x:v>
       </x:c>
       <x:c r="B5" s="22" t="str">
         <x:v>Q2 actual export</x:v>
@@ -578,7 +578,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="23" t="str">
-        <x:v>067-SRC0002</x:v>
+        <x:v>BRD-DATA-0002</x:v>
       </x:c>
       <x:c r="B6" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -612,7 +612,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="23" t="str">
-        <x:v>067-SRC0005</x:v>
+        <x:v>BRD-DATA-0003</x:v>
       </x:c>
       <x:c r="B7" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -648,7 +648,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
-        <x:v>067-SRC0006</x:v>
+        <x:v>BRD-DATA-0004</x:v>
       </x:c>
       <x:c r="B8" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -682,7 +682,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="23" t="str">
-        <x:v>067-SRC0009</x:v>
+        <x:v>BRD-DATA-0005</x:v>
       </x:c>
       <x:c r="B9" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -718,7 +718,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="23" t="str">
-        <x:v>067-SRC0010</x:v>
+        <x:v>BRD-DATA-0006</x:v>
       </x:c>
       <x:c r="B10" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -752,7 +752,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="23" t="str">
-        <x:v>067-SRC0013</x:v>
+        <x:v>BRD-DATA-0007</x:v>
       </x:c>
       <x:c r="B11" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -788,7 +788,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="23" t="str">
-        <x:v>067-SRC0014</x:v>
+        <x:v>BRD-DATA-0008</x:v>
       </x:c>
       <x:c r="B12" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -822,7 +822,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="23" t="str">
-        <x:v>067-SRC0017</x:v>
+        <x:v>BRD-DATA-0009</x:v>
       </x:c>
       <x:c r="B13" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -858,7 +858,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="23" t="str">
-        <x:v>067-SRC0018</x:v>
+        <x:v>BRD-DATA-0010</x:v>
       </x:c>
       <x:c r="B14" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -892,7 +892,7 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="23" t="str">
-        <x:v>067-SRC0021</x:v>
+        <x:v>BRD-DATA-0011</x:v>
       </x:c>
       <x:c r="B15" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -928,7 +928,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="23" t="str">
-        <x:v>067-SRC0022</x:v>
+        <x:v>BRD-DATA-0012</x:v>
       </x:c>
       <x:c r="B16" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -962,7 +962,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="23" t="str">
-        <x:v>067-SRC0025</x:v>
+        <x:v>BRD-DATA-0013</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -998,7 +998,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="23" t="str">
-        <x:v>067-SRC0026</x:v>
+        <x:v>BRD-DATA-0014</x:v>
       </x:c>
       <x:c r="B18" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -1032,7 +1032,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="23" t="str">
-        <x:v>067-SRC0029</x:v>
+        <x:v>BRD-DATA-0015</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -1068,7 +1068,7 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="23" t="str">
-        <x:v>067-SRC0030</x:v>
+        <x:v>BRD-DATA-0016</x:v>
       </x:c>
       <x:c r="B20" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -1102,7 +1102,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="23" t="str">
-        <x:v>067-SRC0033</x:v>
+        <x:v>BRD-DATA-0017</x:v>
       </x:c>
       <x:c r="B21" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -1138,7 +1138,7 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="23" t="str">
-        <x:v>067-SRC0034</x:v>
+        <x:v>BRD-DATA-0018</x:v>
       </x:c>
       <x:c r="B22" s="23" t="str">
         <x:v>Q2 actual export</x:v>
@@ -1172,7 +1172,7 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="23" t="str">
-        <x:v>067-SRC0037</x:v>
+        <x:v>BRD-DATA-0019</x:v>
       </x:c>
       <x:c r="B23" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1184,7 +1184,7 @@
         <x:v>2026-04</x:v>
       </x:c>
       <x:c r="E23" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F23" s="23" t="str">
         <x:v>Operating cash flow</x:v>
@@ -1197,7 +1197,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J23" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K23" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1206,7 +1206,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="23" t="str">
-        <x:v>067-SRC0038</x:v>
+        <x:v>BRD-DATA-0020</x:v>
       </x:c>
       <x:c r="B24" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1218,7 +1218,7 @@
         <x:v>2026-04</x:v>
       </x:c>
       <x:c r="E24" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F24" s="23" t="str">
         <x:v>Capital expenditure</x:v>
@@ -1231,7 +1231,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J24" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K24" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1240,7 +1240,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="23" t="str">
-        <x:v>067-SRC0039</x:v>
+        <x:v>BRD-DATA-0021</x:v>
       </x:c>
       <x:c r="B25" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1252,7 +1252,7 @@
         <x:v>2026-04</x:v>
       </x:c>
       <x:c r="E25" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F25" s="23" t="str">
         <x:v>Free cash flow plan</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J25" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K25" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1274,7 +1274,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="23" t="str">
-        <x:v>067-SRC0040</x:v>
+        <x:v>BRD-DATA-0022</x:v>
       </x:c>
       <x:c r="B26" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>2026-05</x:v>
       </x:c>
       <x:c r="E26" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F26" s="23" t="str">
         <x:v>Operating cash flow</x:v>
@@ -1299,7 +1299,7 @@
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J26" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K26" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1308,7 +1308,7 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="23" t="str">
-        <x:v>067-SRC0041</x:v>
+        <x:v>BRD-DATA-0023</x:v>
       </x:c>
       <x:c r="B27" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1320,7 +1320,7 @@
         <x:v>2026-05</x:v>
       </x:c>
       <x:c r="E27" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F27" s="23" t="str">
         <x:v>Capital expenditure</x:v>
@@ -1333,7 +1333,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J27" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K27" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1342,7 +1342,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="23" t="str">
-        <x:v>067-SRC0042</x:v>
+        <x:v>BRD-DATA-0024</x:v>
       </x:c>
       <x:c r="B28" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1354,7 +1354,7 @@
         <x:v>2026-05</x:v>
       </x:c>
       <x:c r="E28" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F28" s="23" t="str">
         <x:v>Free cash flow plan</x:v>
@@ -1367,7 +1367,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J28" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K28" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1376,7 +1376,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="23" t="str">
-        <x:v>067-SRC0043</x:v>
+        <x:v>BRD-DATA-0025</x:v>
       </x:c>
       <x:c r="B29" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1388,7 +1388,7 @@
         <x:v>2026-06</x:v>
       </x:c>
       <x:c r="E29" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F29" s="23" t="str">
         <x:v>Operating cash flow</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J29" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K29" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1410,7 +1410,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="23" t="str">
-        <x:v>067-SRC0044</x:v>
+        <x:v>BRD-DATA-0026</x:v>
       </x:c>
       <x:c r="B30" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1422,7 +1422,7 @@
         <x:v>2026-06</x:v>
       </x:c>
       <x:c r="E30" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F30" s="23" t="str">
         <x:v>Capital expenditure</x:v>
@@ -1435,7 +1435,7 @@
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J30" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K30" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1444,7 +1444,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="23" t="str">
-        <x:v>067-SRC0045</x:v>
+        <x:v>BRD-DATA-0027</x:v>
       </x:c>
       <x:c r="B31" s="23" t="str">
         <x:v>Cash and capital</x:v>
@@ -1456,7 +1456,7 @@
         <x:v>2026-06</x:v>
       </x:c>
       <x:c r="E31" s="23" t="str">
-        <x:v>Approved case</x:v>
+        <x:v>Board plan</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
         <x:v>Free cash flow plan</x:v>
@@ -1469,7 +1469,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J31" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Approved Q2 cash plan</x:v>
       </x:c>
       <x:c r="K31" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1478,7 +1478,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="23" t="str">
-        <x:v>067-SRC0048</x:v>
+        <x:v>BRD-DATA-0028</x:v>
       </x:c>
       <x:c r="B32" s="23" t="str">
         <x:v>Full-year outlook</x:v>
@@ -1512,25 +1512,25 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="23" t="str">
-        <x:v>067-SRC0049</x:v>
+        <x:v>BRD-DATA-0029</x:v>
       </x:c>
       <x:c r="B33" s="23" t="str">
-        <x:v>Performance diagnostics</x:v>
+        <x:v>Liquidity</x:v>
       </x:c>
       <x:c r="C33" s="23" t="str">
-        <x:v>Construction gross profit</x:v>
+        <x:v>Revolver</x:v>
       </x:c>
       <x:c r="D33" s="23" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>FY27 downside</x:v>
       </x:c>
       <x:c r="E33" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F33" s="23" t="str">
-        <x:v>Unfavorable EBITDA impact</x:v>
+        <x:v>Maximum revolver</x:v>
       </x:c>
       <x:c r="G33" s="26" t="n">
-        <x:v>410000</x:v>
+        <x:v>5350000</x:v>
       </x:c>
       <x:c r="H33" s="23" t="str"/>
       <x:c r="I33" s="23" t="str">
@@ -1546,32 +1546,32 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="23" t="str">
-        <x:v>067-SRC0050</x:v>
+        <x:v>BRD-DATA-0030</x:v>
       </x:c>
       <x:c r="B34" s="23" t="str">
-        <x:v>Performance diagnostics</x:v>
+        <x:v>Q2 actual cash detail</x:v>
       </x:c>
       <x:c r="C34" s="23" t="str">
-        <x:v>Service labor productivity</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="D34" s="23" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2026-04</x:v>
       </x:c>
       <x:c r="E34" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F34" s="23" t="str">
-        <x:v>Unfavorable EBITDA impact</x:v>
+        <x:v>Operating cash flow</x:v>
       </x:c>
       <x:c r="G34" s="26" t="n">
-        <x:v>285000</x:v>
+        <x:v>510000</x:v>
       </x:c>
       <x:c r="H34" s="23" t="str"/>
       <x:c r="I34" s="23" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J34" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Controller cash-flow close schedule</x:v>
       </x:c>
       <x:c r="K34" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1580,32 +1580,32 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="23" t="str">
-        <x:v>067-SRC0051</x:v>
+        <x:v>BRD-DATA-0031</x:v>
       </x:c>
       <x:c r="B35" s="23" t="str">
-        <x:v>Performance diagnostics</x:v>
+        <x:v>Q2 actual cash detail</x:v>
       </x:c>
       <x:c r="C35" s="23" t="str">
-        <x:v>Collections timing</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="D35" s="23" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2026-04</x:v>
       </x:c>
       <x:c r="E35" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F35" s="23" t="str">
-        <x:v>Unfavorable cash impact</x:v>
+        <x:v>Capital expenditure</x:v>
       </x:c>
       <x:c r="G35" s="26" t="n">
-        <x:v>360000</x:v>
+        <x:v>220000</x:v>
       </x:c>
       <x:c r="H35" s="23" t="str"/>
       <x:c r="I35" s="23" t="str">
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J35" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Controller cash-flow close schedule</x:v>
       </x:c>
       <x:c r="K35" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1614,32 +1614,32 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="23" t="str">
-        <x:v>067-SRC0052</x:v>
+        <x:v>BRD-DATA-0032</x:v>
       </x:c>
       <x:c r="B36" s="23" t="str">
-        <x:v>Performance diagnostics</x:v>
+        <x:v>Q2 actual cash detail</x:v>
       </x:c>
       <x:c r="C36" s="23" t="str">
-        <x:v>Controls mix</x:v>
+        <x:v>Alder Ridge</x:v>
       </x:c>
       <x:c r="D36" s="23" t="str">
-        <x:v>2026-Q2</x:v>
+        <x:v>2026-05</x:v>
       </x:c>
       <x:c r="E36" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F36" s="23" t="str">
-        <x:v>Unfavorable EBITDA impact</x:v>
+        <x:v>Operating cash flow</x:v>
       </x:c>
       <x:c r="G36" s="26" t="n">
-        <x:v>95</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="H36" s="23" t="str"/>
       <x:c r="I36" s="23" t="str">
         <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J36" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Controller cash-flow close schedule</x:v>
       </x:c>
       <x:c r="K36" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -1647,38 +1647,106 @@
       <x:c r="L36" s="23" t="str"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="24" t="str">
-        <x:v>067-SRC0053</x:v>
-      </x:c>
-      <x:c r="B37" s="24" t="str">
-        <x:v>Liquidity</x:v>
-      </x:c>
-      <x:c r="C37" s="24" t="str">
-        <x:v>Revolver</x:v>
-      </x:c>
-      <x:c r="D37" s="24" t="str">
-        <x:v>FY27 downside</x:v>
-      </x:c>
-      <x:c r="E37" s="24" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F37" s="24" t="str">
-        <x:v>Maximum revolver</x:v>
-      </x:c>
-      <x:c r="G37" s="27" t="n">
-        <x:v>5350000</x:v>
-      </x:c>
-      <x:c r="H37" s="24" t="str"/>
-      <x:c r="I37" s="24" t="str">
+      <x:c r="A37" s="23" t="str">
+        <x:v>BRD-DATA-0033</x:v>
+      </x:c>
+      <x:c r="B37" s="23" t="str">
+        <x:v>Q2 actual cash detail</x:v>
+      </x:c>
+      <x:c r="C37" s="23" t="str">
+        <x:v>Alder Ridge</x:v>
+      </x:c>
+      <x:c r="D37" s="23" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="E37" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F37" s="23" t="str">
+        <x:v>Capital expenditure</x:v>
+      </x:c>
+      <x:c r="G37" s="26" t="n">
+        <x:v>235000</x:v>
+      </x:c>
+      <x:c r="H37" s="23" t="str"/>
+      <x:c r="I37" s="23" t="str">
         <x:v>USD</x:v>
       </x:c>
-      <x:c r="J37" s="24" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K37" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L37" s="24" t="str"/>
+      <x:c r="J37" s="23" t="str">
+        <x:v>Controller cash-flow close schedule</x:v>
+      </x:c>
+      <x:c r="K37" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L37" s="23" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="23" t="str">
+        <x:v>BRD-DATA-0034</x:v>
+      </x:c>
+      <x:c r="B38" s="23" t="str">
+        <x:v>Q2 actual cash detail</x:v>
+      </x:c>
+      <x:c r="C38" s="23" t="str">
+        <x:v>Alder Ridge</x:v>
+      </x:c>
+      <x:c r="D38" s="23" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="E38" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F38" s="23" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="G38" s="26" t="n">
+        <x:v>820000</x:v>
+      </x:c>
+      <x:c r="H38" s="23" t="str"/>
+      <x:c r="I38" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J38" s="23" t="str">
+        <x:v>Controller cash-flow close schedule</x:v>
+      </x:c>
+      <x:c r="K38" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L38" s="23" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="24" t="str">
+        <x:v>BRD-DATA-0035</x:v>
+      </x:c>
+      <x:c r="B39" s="24" t="str">
+        <x:v>Q2 actual cash detail</x:v>
+      </x:c>
+      <x:c r="C39" s="24" t="str">
+        <x:v>Alder Ridge</x:v>
+      </x:c>
+      <x:c r="D39" s="24" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="E39" s="24" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F39" s="24" t="str">
+        <x:v>Capital expenditure</x:v>
+      </x:c>
+      <x:c r="G39" s="27" t="n">
+        <x:v>270000</x:v>
+      </x:c>
+      <x:c r="H39" s="24" t="str"/>
+      <x:c r="I39" s="24" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J39" s="24" t="str">
+        <x:v>Controller cash-flow close schedule</x:v>
+      </x:c>
+      <x:c r="K39" s="30" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L39" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1709,7 +1777,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the Q2 board performance dashboard | Approved Plan</x:v>
+        <x:v>Q2 board performance dashboard | Approved Plan</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1725,7 +1793,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>LOCKED INPUT SCHEDULE • refreshed from current management workbooks and Vista ERP • Do not edit</x:v>
+        <x:v>REFERENCE SCHEDULE • source and date retained • do not edit</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -1779,7 +1847,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="22" t="str">
-        <x:v>067-SRC0003</x:v>
+        <x:v>BRD-PLAN-0001</x:v>
       </x:c>
       <x:c r="B5" s="22" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -1804,16 +1872,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J5" s="22" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K5" s="28" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L5" s="22" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="23" t="str">
-        <x:v>067-SRC0004</x:v>
+        <x:v>BRD-PLAN-0002</x:v>
       </x:c>
       <x:c r="B6" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -1838,16 +1906,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J6" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K6" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L6" s="23" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="23" t="str">
-        <x:v>067-SRC0007</x:v>
+        <x:v>BRD-PLAN-0003</x:v>
       </x:c>
       <x:c r="B7" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -1872,16 +1940,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J7" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K7" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L7" s="23" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="23" t="str">
-        <x:v>067-SRC0008</x:v>
+        <x:v>BRD-PLAN-0004</x:v>
       </x:c>
       <x:c r="B8" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -1906,16 +1974,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J8" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K8" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L8" s="23" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="23" t="str">
-        <x:v>067-SRC0011</x:v>
+        <x:v>BRD-PLAN-0005</x:v>
       </x:c>
       <x:c r="B9" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -1940,16 +2008,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J9" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K9" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L9" s="23" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="23" t="str">
-        <x:v>067-SRC0012</x:v>
+        <x:v>BRD-PLAN-0006</x:v>
       </x:c>
       <x:c r="B10" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -1974,16 +2042,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J10" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K10" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L10" s="23" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="23" t="str">
-        <x:v>067-SRC0015</x:v>
+        <x:v>BRD-PLAN-0007</x:v>
       </x:c>
       <x:c r="B11" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2008,16 +2076,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J11" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K11" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L11" s="23" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="23" t="str">
-        <x:v>067-SRC0016</x:v>
+        <x:v>BRD-PLAN-0008</x:v>
       </x:c>
       <x:c r="B12" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2042,16 +2110,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J12" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K12" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L12" s="23" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="23" t="str">
-        <x:v>067-SRC0019</x:v>
+        <x:v>BRD-PLAN-0009</x:v>
       </x:c>
       <x:c r="B13" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2076,16 +2144,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J13" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K13" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L13" s="23" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="23" t="str">
-        <x:v>067-SRC0020</x:v>
+        <x:v>BRD-PLAN-0010</x:v>
       </x:c>
       <x:c r="B14" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2110,16 +2178,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J14" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K14" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L14" s="23" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="23" t="str">
-        <x:v>067-SRC0023</x:v>
+        <x:v>BRD-PLAN-0011</x:v>
       </x:c>
       <x:c r="B15" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2144,16 +2212,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J15" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K15" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L15" s="23" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="23" t="str">
-        <x:v>067-SRC0024</x:v>
+        <x:v>BRD-PLAN-0012</x:v>
       </x:c>
       <x:c r="B16" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2178,16 +2246,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J16" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K16" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L16" s="23" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="23" t="str">
-        <x:v>067-SRC0027</x:v>
+        <x:v>BRD-PLAN-0013</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2212,16 +2280,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J17" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K17" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L17" s="23" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="23" t="str">
-        <x:v>067-SRC0028</x:v>
+        <x:v>BRD-PLAN-0014</x:v>
       </x:c>
       <x:c r="B18" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2246,16 +2314,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J18" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K18" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L18" s="23" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="23" t="str">
-        <x:v>067-SRC0031</x:v>
+        <x:v>BRD-PLAN-0015</x:v>
       </x:c>
       <x:c r="B19" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2280,16 +2348,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J19" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K19" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L19" s="23" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="23" t="str">
-        <x:v>067-SRC0032</x:v>
+        <x:v>BRD-PLAN-0016</x:v>
       </x:c>
       <x:c r="B20" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2314,16 +2382,16 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J20" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K20" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L20" s="23" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="23" t="str">
-        <x:v>067-SRC0035</x:v>
+        <x:v>BRD-PLAN-0017</x:v>
       </x:c>
       <x:c r="B21" s="23" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2348,16 +2416,16 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="J21" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K21" s="29" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L21" s="23" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="24" t="str">
-        <x:v>067-SRC0036</x:v>
+        <x:v>BRD-PLAN-0018</x:v>
       </x:c>
       <x:c r="B22" s="24" t="str">
         <x:v>Q2 approved plan</x:v>
@@ -2382,10 +2450,10 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="J22" s="24" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 management comparator approved 2026-03-31</x:v>
       </x:c>
       <x:c r="K22" s="30" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="L22" s="24" t="str"/>
     </x:row>
@@ -2414,7 +2482,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the Q2 board performance dashboard | Executive Summary</x:v>
+        <x:v>Q2 board performance dashboard | Executive Summary</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -2426,7 +2494,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>WORKING DASHBOARD • build formula-linked analysis from the protected source tabs</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -2438,205 +2506,149 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Period / Scenario</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Business unit / item</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Input / driver</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Formula output</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Source / file / ref</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="str">
+        <x:v>Check</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>q2_revenue</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="33"/>
+      <x:c r="B5" s="33"/>
+      <x:c r="C5" s="33"/>
+      <x:c r="D5" s="33"/>
+      <x:c r="E5" s="33"/>
+      <x:c r="F5" s="33"/>
+      <x:c r="G5" s="33"/>
+      <x:c r="H5" s="33"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>q2_ebitda</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="34"/>
+      <x:c r="B6" s="34"/>
+      <x:c r="C6" s="34"/>
+      <x:c r="D6" s="34"/>
+      <x:c r="E6" s="34"/>
+      <x:c r="F6" s="34"/>
+      <x:c r="G6" s="34"/>
+      <x:c r="H6" s="34"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>q2_free_cash_flow</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="34"/>
+      <x:c r="B7" s="34"/>
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34"/>
+      <x:c r="E7" s="34"/>
+      <x:c r="F7" s="34"/>
+      <x:c r="G7" s="34"/>
+      <x:c r="H7" s="34"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>latest_full_year_revenue_outlook</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
+      <x:c r="A8" s="34"/>
+      <x:c r="B8" s="34"/>
+      <x:c r="C8" s="34"/>
+      <x:c r="D8" s="34"/>
+      <x:c r="E8" s="34"/>
+      <x:c r="F8" s="34"/>
+      <x:c r="G8" s="34"/>
+      <x:c r="H8" s="34"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>q2_revenue_variance</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
+      <x:c r="A9" s="34"/>
+      <x:c r="B9" s="34"/>
+      <x:c r="C9" s="34"/>
+      <x:c r="D9" s="34"/>
+      <x:c r="E9" s="34"/>
+      <x:c r="F9" s="34"/>
+      <x:c r="G9" s="34"/>
+      <x:c r="H9" s="34"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>q2_ebitda_variance</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
+      <x:c r="A10" s="34"/>
+      <x:c r="B10" s="34"/>
+      <x:c r="C10" s="34"/>
+      <x:c r="D10" s="34"/>
+      <x:c r="E10" s="34"/>
+      <x:c r="F10" s="34"/>
+      <x:c r="G10" s="34"/>
+      <x:c r="H10" s="34"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>q2_free_cash_flow_variance</x:v>
-      </x:c>
-      <x:c r="B11" s="36"/>
+      <x:c r="A11" s="34"/>
+      <x:c r="B11" s="34"/>
+      <x:c r="C11" s="34"/>
+      <x:c r="D11" s="34"/>
+      <x:c r="E11" s="34"/>
+      <x:c r="F11" s="34"/>
+      <x:c r="G11" s="34"/>
+      <x:c r="H11" s="34"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="34" t="str">
-        <x:v>largest_financial_misses</x:v>
-      </x:c>
-      <x:c r="B12" s="37"/>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B15" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H15" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
+      <x:c r="A12" s="34"/>
+      <x:c r="B12" s="34"/>
+      <x:c r="C12" s="34"/>
+      <x:c r="D12" s="34"/>
+      <x:c r="E12" s="34"/>
+      <x:c r="F12" s="34"/>
+      <x:c r="G12" s="34"/>
+      <x:c r="H12" s="34"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="34"/>
+      <x:c r="B13" s="34"/>
+      <x:c r="C13" s="34"/>
+      <x:c r="D13" s="34"/>
+      <x:c r="E13" s="34"/>
+      <x:c r="F13" s="34"/>
+      <x:c r="G13" s="34"/>
+      <x:c r="H13" s="34"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="34"/>
+      <x:c r="B14" s="34"/>
+      <x:c r="C14" s="34"/>
+      <x:c r="D14" s="34"/>
+      <x:c r="E14" s="34"/>
+      <x:c r="F14" s="34"/>
+      <x:c r="G14" s="34"/>
+      <x:c r="H14" s="34"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="34"/>
+      <x:c r="B15" s="34"/>
+      <x:c r="C15" s="34"/>
+      <x:c r="D15" s="34"/>
+      <x:c r="E15" s="34"/>
+      <x:c r="F15" s="34"/>
+      <x:c r="G15" s="34"/>
+      <x:c r="H15" s="34"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="40"/>
-      <x:c r="B16" s="40"/>
-      <x:c r="C16" s="40"/>
-      <x:c r="D16" s="40"/>
-      <x:c r="E16" s="40"/>
-      <x:c r="F16" s="40"/>
-      <x:c r="G16" s="40"/>
-      <x:c r="H16" s="40"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="41"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="41"/>
-      <x:c r="E19" s="41"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="41"/>
-      <x:c r="H19" s="41"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="41"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="41"/>
-      <x:c r="E20" s="41"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="41"/>
-      <x:c r="H20" s="41"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="41"/>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="41"/>
-      <x:c r="B22" s="41"/>
-      <x:c r="C22" s="41"/>
-      <x:c r="D22" s="41"/>
-      <x:c r="E22" s="41"/>
-      <x:c r="F22" s="41"/>
-      <x:c r="G22" s="41"/>
-      <x:c r="H22" s="41"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="41"/>
-      <x:c r="B23" s="41"/>
-      <x:c r="C23" s="41"/>
-      <x:c r="D23" s="41"/>
-      <x:c r="E23" s="41"/>
-      <x:c r="F23" s="41"/>
-      <x:c r="G23" s="41"/>
-      <x:c r="H23" s="41"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="41"/>
-      <x:c r="B24" s="41"/>
-      <x:c r="C24" s="41"/>
-      <x:c r="D24" s="41"/>
-      <x:c r="E24" s="41"/>
-      <x:c r="F24" s="41"/>
-      <x:c r="G24" s="41"/>
-      <x:c r="H24" s="41"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="41"/>
-      <x:c r="B25" s="41"/>
-      <x:c r="C25" s="41"/>
-      <x:c r="D25" s="41"/>
-      <x:c r="E25" s="41"/>
-      <x:c r="F25" s="41"/>
-      <x:c r="G25" s="41"/>
-      <x:c r="H25" s="41"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="41"/>
-      <x:c r="B26" s="41"/>
-      <x:c r="C26" s="41"/>
-      <x:c r="D26" s="41"/>
-      <x:c r="E26" s="41"/>
-      <x:c r="F26" s="41"/>
-      <x:c r="G26" s="41"/>
-      <x:c r="H26" s="41"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="42"/>
-      <x:c r="B27" s="42"/>
-      <x:c r="C27" s="42"/>
-      <x:c r="D27" s="42"/>
-      <x:c r="E27" s="42"/>
-      <x:c r="F27" s="42"/>
-      <x:c r="G27" s="42"/>
-      <x:c r="H27" s="42"/>
+      <x:c r="A16" s="35"/>
+      <x:c r="B16" s="35"/>
+      <x:c r="C16" s="35"/>
+      <x:c r="D16" s="35"/>
+      <x:c r="E16" s="35"/>
+      <x:c r="F16" s="35"/>
+      <x:c r="G16" s="35"/>
+      <x:c r="H16" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2663,7 +2675,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the Q2 board performance dashboard | Business Units</x:v>
+        <x:v>Q2 board performance dashboard | Business Units</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -2675,7 +2687,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>WORKING DASHBOARD • build formula-linked analysis from the protected source tabs</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -2687,205 +2699,149 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Period / Scenario</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Business unit / item</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Input / driver</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Formula output</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Source / file / ref</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="str">
+        <x:v>Check</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>q2_revenue</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="33"/>
+      <x:c r="B5" s="33"/>
+      <x:c r="C5" s="33"/>
+      <x:c r="D5" s="33"/>
+      <x:c r="E5" s="33"/>
+      <x:c r="F5" s="33"/>
+      <x:c r="G5" s="33"/>
+      <x:c r="H5" s="33"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>q2_ebitda</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="34"/>
+      <x:c r="B6" s="34"/>
+      <x:c r="C6" s="34"/>
+      <x:c r="D6" s="34"/>
+      <x:c r="E6" s="34"/>
+      <x:c r="F6" s="34"/>
+      <x:c r="G6" s="34"/>
+      <x:c r="H6" s="34"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>q2_free_cash_flow</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="34"/>
+      <x:c r="B7" s="34"/>
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34"/>
+      <x:c r="E7" s="34"/>
+      <x:c r="F7" s="34"/>
+      <x:c r="G7" s="34"/>
+      <x:c r="H7" s="34"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>latest_full_year_revenue_outlook</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
+      <x:c r="A8" s="34"/>
+      <x:c r="B8" s="34"/>
+      <x:c r="C8" s="34"/>
+      <x:c r="D8" s="34"/>
+      <x:c r="E8" s="34"/>
+      <x:c r="F8" s="34"/>
+      <x:c r="G8" s="34"/>
+      <x:c r="H8" s="34"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>q2_revenue_variance</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
+      <x:c r="A9" s="34"/>
+      <x:c r="B9" s="34"/>
+      <x:c r="C9" s="34"/>
+      <x:c r="D9" s="34"/>
+      <x:c r="E9" s="34"/>
+      <x:c r="F9" s="34"/>
+      <x:c r="G9" s="34"/>
+      <x:c r="H9" s="34"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>q2_ebitda_variance</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
+      <x:c r="A10" s="34"/>
+      <x:c r="B10" s="34"/>
+      <x:c r="C10" s="34"/>
+      <x:c r="D10" s="34"/>
+      <x:c r="E10" s="34"/>
+      <x:c r="F10" s="34"/>
+      <x:c r="G10" s="34"/>
+      <x:c r="H10" s="34"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>q2_free_cash_flow_variance</x:v>
-      </x:c>
-      <x:c r="B11" s="36"/>
+      <x:c r="A11" s="34"/>
+      <x:c r="B11" s="34"/>
+      <x:c r="C11" s="34"/>
+      <x:c r="D11" s="34"/>
+      <x:c r="E11" s="34"/>
+      <x:c r="F11" s="34"/>
+      <x:c r="G11" s="34"/>
+      <x:c r="H11" s="34"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="34" t="str">
-        <x:v>largest_financial_misses</x:v>
-      </x:c>
-      <x:c r="B12" s="37"/>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B15" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H15" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
+      <x:c r="A12" s="34"/>
+      <x:c r="B12" s="34"/>
+      <x:c r="C12" s="34"/>
+      <x:c r="D12" s="34"/>
+      <x:c r="E12" s="34"/>
+      <x:c r="F12" s="34"/>
+      <x:c r="G12" s="34"/>
+      <x:c r="H12" s="34"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="34"/>
+      <x:c r="B13" s="34"/>
+      <x:c r="C13" s="34"/>
+      <x:c r="D13" s="34"/>
+      <x:c r="E13" s="34"/>
+      <x:c r="F13" s="34"/>
+      <x:c r="G13" s="34"/>
+      <x:c r="H13" s="34"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="34"/>
+      <x:c r="B14" s="34"/>
+      <x:c r="C14" s="34"/>
+      <x:c r="D14" s="34"/>
+      <x:c r="E14" s="34"/>
+      <x:c r="F14" s="34"/>
+      <x:c r="G14" s="34"/>
+      <x:c r="H14" s="34"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="34"/>
+      <x:c r="B15" s="34"/>
+      <x:c r="C15" s="34"/>
+      <x:c r="D15" s="34"/>
+      <x:c r="E15" s="34"/>
+      <x:c r="F15" s="34"/>
+      <x:c r="G15" s="34"/>
+      <x:c r="H15" s="34"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="40"/>
-      <x:c r="B16" s="40"/>
-      <x:c r="C16" s="40"/>
-      <x:c r="D16" s="40"/>
-      <x:c r="E16" s="40"/>
-      <x:c r="F16" s="40"/>
-      <x:c r="G16" s="40"/>
-      <x:c r="H16" s="40"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="41"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="41"/>
-      <x:c r="E19" s="41"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="41"/>
-      <x:c r="H19" s="41"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="41"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="41"/>
-      <x:c r="E20" s="41"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="41"/>
-      <x:c r="H20" s="41"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="41"/>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="41"/>
-      <x:c r="B22" s="41"/>
-      <x:c r="C22" s="41"/>
-      <x:c r="D22" s="41"/>
-      <x:c r="E22" s="41"/>
-      <x:c r="F22" s="41"/>
-      <x:c r="G22" s="41"/>
-      <x:c r="H22" s="41"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="41"/>
-      <x:c r="B23" s="41"/>
-      <x:c r="C23" s="41"/>
-      <x:c r="D23" s="41"/>
-      <x:c r="E23" s="41"/>
-      <x:c r="F23" s="41"/>
-      <x:c r="G23" s="41"/>
-      <x:c r="H23" s="41"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="41"/>
-      <x:c r="B24" s="41"/>
-      <x:c r="C24" s="41"/>
-      <x:c r="D24" s="41"/>
-      <x:c r="E24" s="41"/>
-      <x:c r="F24" s="41"/>
-      <x:c r="G24" s="41"/>
-      <x:c r="H24" s="41"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="41"/>
-      <x:c r="B25" s="41"/>
-      <x:c r="C25" s="41"/>
-      <x:c r="D25" s="41"/>
-      <x:c r="E25" s="41"/>
-      <x:c r="F25" s="41"/>
-      <x:c r="G25" s="41"/>
-      <x:c r="H25" s="41"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="41"/>
-      <x:c r="B26" s="41"/>
-      <x:c r="C26" s="41"/>
-      <x:c r="D26" s="41"/>
-      <x:c r="E26" s="41"/>
-      <x:c r="F26" s="41"/>
-      <x:c r="G26" s="41"/>
-      <x:c r="H26" s="41"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="42"/>
-      <x:c r="B27" s="42"/>
-      <x:c r="C27" s="42"/>
-      <x:c r="D27" s="42"/>
-      <x:c r="E27" s="42"/>
-      <x:c r="F27" s="42"/>
-      <x:c r="G27" s="42"/>
-      <x:c r="H27" s="42"/>
+      <x:c r="A16" s="35"/>
+      <x:c r="B16" s="35"/>
+      <x:c r="C16" s="35"/>
+      <x:c r="D16" s="35"/>
+      <x:c r="E16" s="35"/>
+      <x:c r="F16" s="35"/>
+      <x:c r="G16" s="35"/>
+      <x:c r="H16" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2912,7 +2868,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the Q2 board performance dashboard | Cash &amp; Capital</x:v>
+        <x:v>Q2 board performance dashboard | Cash &amp; Capital</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -2924,7 +2880,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>WORKING DASHBOARD • build formula-linked analysis from the protected source tabs</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -2936,205 +2892,149 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="15" t="str">
-        <x:v>Required headline output</x:v>
-      </x:c>
-      <x:c r="B4" s="17" t="str">
-        <x:v>Formula-driven result</x:v>
+        <x:v>Period / Scenario</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Business unit / item</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="D4" s="16" t="str">
+        <x:v>Input / driver</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Formula output</x:v>
+      </x:c>
+      <x:c r="F4" s="16" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
+        <x:v>Source / file / ref</x:v>
+      </x:c>
+      <x:c r="H4" s="17" t="str">
+        <x:v>Check</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
-        <x:v>q2_revenue</x:v>
-      </x:c>
-      <x:c r="B5" s="35"/>
+      <x:c r="A5" s="33"/>
+      <x:c r="B5" s="33"/>
+      <x:c r="C5" s="33"/>
+      <x:c r="D5" s="33"/>
+      <x:c r="E5" s="33"/>
+      <x:c r="F5" s="33"/>
+      <x:c r="G5" s="33"/>
+      <x:c r="H5" s="33"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>q2_ebitda</x:v>
-      </x:c>
-      <x:c r="B6" s="36"/>
+      <x:c r="A6" s="34"/>
+      <x:c r="B6" s="34"/>
+      <x:c r="C6" s="34"/>
+      <x:c r="D6" s="34"/>
+      <x:c r="E6" s="34"/>
+      <x:c r="F6" s="34"/>
+      <x:c r="G6" s="34"/>
+      <x:c r="H6" s="34"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>q2_free_cash_flow</x:v>
-      </x:c>
-      <x:c r="B7" s="36"/>
+      <x:c r="A7" s="34"/>
+      <x:c r="B7" s="34"/>
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34"/>
+      <x:c r="E7" s="34"/>
+      <x:c r="F7" s="34"/>
+      <x:c r="G7" s="34"/>
+      <x:c r="H7" s="34"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>latest_full_year_revenue_outlook</x:v>
-      </x:c>
-      <x:c r="B8" s="36"/>
+      <x:c r="A8" s="34"/>
+      <x:c r="B8" s="34"/>
+      <x:c r="C8" s="34"/>
+      <x:c r="D8" s="34"/>
+      <x:c r="E8" s="34"/>
+      <x:c r="F8" s="34"/>
+      <x:c r="G8" s="34"/>
+      <x:c r="H8" s="34"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>q2_revenue_variance</x:v>
-      </x:c>
-      <x:c r="B9" s="36"/>
+      <x:c r="A9" s="34"/>
+      <x:c r="B9" s="34"/>
+      <x:c r="C9" s="34"/>
+      <x:c r="D9" s="34"/>
+      <x:c r="E9" s="34"/>
+      <x:c r="F9" s="34"/>
+      <x:c r="G9" s="34"/>
+      <x:c r="H9" s="34"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>q2_ebitda_variance</x:v>
-      </x:c>
-      <x:c r="B10" s="36"/>
+      <x:c r="A10" s="34"/>
+      <x:c r="B10" s="34"/>
+      <x:c r="C10" s="34"/>
+      <x:c r="D10" s="34"/>
+      <x:c r="E10" s="34"/>
+      <x:c r="F10" s="34"/>
+      <x:c r="G10" s="34"/>
+      <x:c r="H10" s="34"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>q2_free_cash_flow_variance</x:v>
-      </x:c>
-      <x:c r="B11" s="36"/>
+      <x:c r="A11" s="34"/>
+      <x:c r="B11" s="34"/>
+      <x:c r="C11" s="34"/>
+      <x:c r="D11" s="34"/>
+      <x:c r="E11" s="34"/>
+      <x:c r="F11" s="34"/>
+      <x:c r="G11" s="34"/>
+      <x:c r="H11" s="34"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="34" t="str">
-        <x:v>largest_financial_misses</x:v>
-      </x:c>
-      <x:c r="B12" s="37"/>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="15" t="str">
-        <x:v>Period / Scenario</x:v>
-      </x:c>
-      <x:c r="B15" s="16" t="str">
-        <x:v>Business unit / item</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="str">
-        <x:v>Metric</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="str">
-        <x:v>Input / driver</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="str">
-        <x:v>Formula output</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="str">
-        <x:v>Source / file / ref</x:v>
-      </x:c>
-      <x:c r="H15" s="17" t="str">
-        <x:v>Check</x:v>
-      </x:c>
+      <x:c r="A12" s="34"/>
+      <x:c r="B12" s="34"/>
+      <x:c r="C12" s="34"/>
+      <x:c r="D12" s="34"/>
+      <x:c r="E12" s="34"/>
+      <x:c r="F12" s="34"/>
+      <x:c r="G12" s="34"/>
+      <x:c r="H12" s="34"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="34"/>
+      <x:c r="B13" s="34"/>
+      <x:c r="C13" s="34"/>
+      <x:c r="D13" s="34"/>
+      <x:c r="E13" s="34"/>
+      <x:c r="F13" s="34"/>
+      <x:c r="G13" s="34"/>
+      <x:c r="H13" s="34"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="34"/>
+      <x:c r="B14" s="34"/>
+      <x:c r="C14" s="34"/>
+      <x:c r="D14" s="34"/>
+      <x:c r="E14" s="34"/>
+      <x:c r="F14" s="34"/>
+      <x:c r="G14" s="34"/>
+      <x:c r="H14" s="34"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="34"/>
+      <x:c r="B15" s="34"/>
+      <x:c r="C15" s="34"/>
+      <x:c r="D15" s="34"/>
+      <x:c r="E15" s="34"/>
+      <x:c r="F15" s="34"/>
+      <x:c r="G15" s="34"/>
+      <x:c r="H15" s="34"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="40"/>
-      <x:c r="B16" s="40"/>
-      <x:c r="C16" s="40"/>
-      <x:c r="D16" s="40"/>
-      <x:c r="E16" s="40"/>
-      <x:c r="F16" s="40"/>
-      <x:c r="G16" s="40"/>
-      <x:c r="H16" s="40"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="41"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="41"/>
-      <x:c r="E19" s="41"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="41"/>
-      <x:c r="H19" s="41"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="41"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="41"/>
-      <x:c r="E20" s="41"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="41"/>
-      <x:c r="H20" s="41"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="41"/>
-      <x:c r="B21" s="41"/>
-      <x:c r="C21" s="41"/>
-      <x:c r="D21" s="41"/>
-      <x:c r="E21" s="41"/>
-      <x:c r="F21" s="41"/>
-      <x:c r="G21" s="41"/>
-      <x:c r="H21" s="41"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="41"/>
-      <x:c r="B22" s="41"/>
-      <x:c r="C22" s="41"/>
-      <x:c r="D22" s="41"/>
-      <x:c r="E22" s="41"/>
-      <x:c r="F22" s="41"/>
-      <x:c r="G22" s="41"/>
-      <x:c r="H22" s="41"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="41"/>
-      <x:c r="B23" s="41"/>
-      <x:c r="C23" s="41"/>
-      <x:c r="D23" s="41"/>
-      <x:c r="E23" s="41"/>
-      <x:c r="F23" s="41"/>
-      <x:c r="G23" s="41"/>
-      <x:c r="H23" s="41"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="41"/>
-      <x:c r="B24" s="41"/>
-      <x:c r="C24" s="41"/>
-      <x:c r="D24" s="41"/>
-      <x:c r="E24" s="41"/>
-      <x:c r="F24" s="41"/>
-      <x:c r="G24" s="41"/>
-      <x:c r="H24" s="41"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="41"/>
-      <x:c r="B25" s="41"/>
-      <x:c r="C25" s="41"/>
-      <x:c r="D25" s="41"/>
-      <x:c r="E25" s="41"/>
-      <x:c r="F25" s="41"/>
-      <x:c r="G25" s="41"/>
-      <x:c r="H25" s="41"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="41"/>
-      <x:c r="B26" s="41"/>
-      <x:c r="C26" s="41"/>
-      <x:c r="D26" s="41"/>
-      <x:c r="E26" s="41"/>
-      <x:c r="F26" s="41"/>
-      <x:c r="G26" s="41"/>
-      <x:c r="H26" s="41"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="42"/>
-      <x:c r="B27" s="42"/>
-      <x:c r="C27" s="42"/>
-      <x:c r="D27" s="42"/>
-      <x:c r="E27" s="42"/>
-      <x:c r="F27" s="42"/>
-      <x:c r="G27" s="42"/>
-      <x:c r="H27" s="42"/>
+      <x:c r="A16" s="35"/>
+      <x:c r="B16" s="35"/>
+      <x:c r="C16" s="35"/>
+      <x:c r="D16" s="35"/>
+      <x:c r="E16" s="35"/>
+      <x:c r="F16" s="35"/>
+      <x:c r="G16" s="35"/>
+      <x:c r="H16" s="35"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3150,7 +3050,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
@@ -3160,7 +3060,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the Q2 board performance dashboard | Checks</x:v>
+        <x:v>Q2 board performance dashboard | Checks</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -3172,7 +3072,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>WORKING DASHBOARD • build formula-linked analysis from the protected source tabs</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3206,81 +3106,81 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="32" t="str">
+      <x:c r="A5" s="37" t="str">
         <x:v>Source population tie</x:v>
       </x:c>
-      <x:c r="B5" s="35"/>
-      <x:c r="C5" s="35"/>
-      <x:c r="D5" s="35"/>
-      <x:c r="E5" s="35"/>
-      <x:c r="F5" s="35"/>
-      <x:c r="G5" s="35"/>
+      <x:c r="B5" s="40"/>
+      <x:c r="C5" s="40"/>
+      <x:c r="D5" s="40"/>
+      <x:c r="E5" s="40"/>
+      <x:c r="F5" s="40"/>
+      <x:c r="G5" s="40"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
+      <x:c r="A6" s="38" t="str">
         <x:v>Current-versus-prior version</x:v>
       </x:c>
-      <x:c r="B6" s="36"/>
-      <x:c r="C6" s="36"/>
-      <x:c r="D6" s="36"/>
-      <x:c r="E6" s="36"/>
-      <x:c r="F6" s="36"/>
-      <x:c r="G6" s="36"/>
+      <x:c r="B6" s="41"/>
+      <x:c r="C6" s="41"/>
+      <x:c r="D6" s="41"/>
+      <x:c r="E6" s="41"/>
+      <x:c r="F6" s="41"/>
+      <x:c r="G6" s="41"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
+      <x:c r="A7" s="38" t="str">
         <x:v>Period completeness</x:v>
       </x:c>
-      <x:c r="B7" s="36"/>
-      <x:c r="C7" s="36"/>
-      <x:c r="D7" s="36"/>
-      <x:c r="E7" s="36"/>
-      <x:c r="F7" s="36"/>
-      <x:c r="G7" s="36"/>
+      <x:c r="B7" s="41"/>
+      <x:c r="C7" s="41"/>
+      <x:c r="D7" s="41"/>
+      <x:c r="E7" s="41"/>
+      <x:c r="F7" s="41"/>
+      <x:c r="G7" s="41"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
+      <x:c r="A8" s="38" t="str">
         <x:v>Scenario validity</x:v>
       </x:c>
-      <x:c r="B8" s="36"/>
-      <x:c r="C8" s="36"/>
-      <x:c r="D8" s="36"/>
-      <x:c r="E8" s="36"/>
-      <x:c r="F8" s="36"/>
-      <x:c r="G8" s="36"/>
+      <x:c r="B8" s="41"/>
+      <x:c r="C8" s="41"/>
+      <x:c r="D8" s="41"/>
+      <x:c r="E8" s="41"/>
+      <x:c r="F8" s="41"/>
+      <x:c r="G8" s="41"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
+      <x:c r="A9" s="38" t="str">
         <x:v>Unit conversion</x:v>
       </x:c>
-      <x:c r="B9" s="36"/>
-      <x:c r="C9" s="36"/>
-      <x:c r="D9" s="36"/>
-      <x:c r="E9" s="36"/>
-      <x:c r="F9" s="36"/>
-      <x:c r="G9" s="36"/>
+      <x:c r="B9" s="41"/>
+      <x:c r="C9" s="41"/>
+      <x:c r="D9" s="41"/>
+      <x:c r="E9" s="41"/>
+      <x:c r="F9" s="41"/>
+      <x:c r="G9" s="41"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
+      <x:c r="A10" s="38" t="str">
         <x:v>Roll-forward / bridge</x:v>
       </x:c>
-      <x:c r="B10" s="36"/>
-      <x:c r="C10" s="36"/>
-      <x:c r="D10" s="36"/>
-      <x:c r="E10" s="36"/>
-      <x:c r="F10" s="36"/>
-      <x:c r="G10" s="36"/>
+      <x:c r="B10" s="41"/>
+      <x:c r="C10" s="41"/>
+      <x:c r="D10" s="41"/>
+      <x:c r="E10" s="41"/>
+      <x:c r="F10" s="41"/>
+      <x:c r="G10" s="41"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="34" t="str">
+      <x:c r="A11" s="39" t="str">
         <x:v>MODEL STATUS</x:v>
       </x:c>
-      <x:c r="B11" s="37"/>
-      <x:c r="C11" s="37"/>
-      <x:c r="D11" s="37"/>
-      <x:c r="E11" s="37"/>
-      <x:c r="F11" s="37"/>
-      <x:c r="G11" s="37"/>
+      <x:c r="B11" s="42"/>
+      <x:c r="C11" s="42"/>
+      <x:c r="D11" s="42"/>
+      <x:c r="E11" s="42"/>
+      <x:c r="F11" s="42"/>
+      <x:c r="G11" s="42"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
